--- a/mejoras.xlsx
+++ b/mejoras.xlsx
@@ -119,12 +119,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,7 +441,7 @@
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -449,7 +450,9 @@
       <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="3">
+        <v>46256</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
